--- a/artfynd/A 978-2026 artfynd.xlsx
+++ b/artfynd/A 978-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154306</v>
       </c>
       <c r="B2" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>131154308</v>
       </c>
       <c r="B3" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>131154307</v>
       </c>
       <c r="B4" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>131187649</v>
       </c>
       <c r="B5" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 978-2026 artfynd.xlsx
+++ b/artfynd/A 978-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154306</v>
       </c>
       <c r="B2" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>131187649</v>
       </c>
       <c r="B5" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 978-2026 artfynd.xlsx
+++ b/artfynd/A 978-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154306</v>
       </c>
       <c r="B2" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>131154308</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>131154307</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>131187649</v>
       </c>
       <c r="B5" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 978-2026 artfynd.xlsx
+++ b/artfynd/A 978-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154306</v>
       </c>
       <c r="B2" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>131154308</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>131154307</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>131187649</v>
       </c>
       <c r="B5" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 978-2026 artfynd.xlsx
+++ b/artfynd/A 978-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154306</v>
       </c>
       <c r="B2" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>131154308</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>131154307</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>131187649</v>
       </c>
       <c r="B5" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 978-2026 artfynd.xlsx
+++ b/artfynd/A 978-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154306</v>
       </c>
       <c r="B2" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>131154308</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>131154307</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>131187649</v>
       </c>
       <c r="B5" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 978-2026 artfynd.xlsx
+++ b/artfynd/A 978-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154306</v>
       </c>
       <c r="B2" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>131154308</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>131154307</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>131187649</v>
       </c>
       <c r="B5" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 978-2026 artfynd.xlsx
+++ b/artfynd/A 978-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154306</v>
       </c>
       <c r="B2" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>131154308</v>
       </c>
       <c r="B3" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>131154307</v>
       </c>
       <c r="B4" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>131187649</v>
       </c>
       <c r="B5" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 978-2026 artfynd.xlsx
+++ b/artfynd/A 978-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154306</v>
       </c>
       <c r="B2" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>131154308</v>
       </c>
       <c r="B3" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>131154307</v>
       </c>
       <c r="B4" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>131187649</v>
       </c>
       <c r="B5" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 978-2026 artfynd.xlsx
+++ b/artfynd/A 978-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131154306</v>
+        <v>131154307</v>
       </c>
       <c r="B2" t="n">
-        <v>91848</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445177</v>
+        <v>445118</v>
       </c>
       <c r="R2" t="n">
-        <v>7052743</v>
+        <v>7052704</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,11 +749,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Fruktkroppar i en stående död gran med full längd och 34 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,12 +778,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -809,11 +804,11 @@
         <v>131154308</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -932,14 +927,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131154307</v>
+        <v>131154309</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -970,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445118</v>
+        <v>445146</v>
       </c>
       <c r="R4" t="n">
-        <v>7052704</v>
+        <v>7052922</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1055,99 +1050,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>131187649</v>
-      </c>
-      <c r="B5" t="n">
-        <v>91848</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Nästflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>445165</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7052703</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 978-2026 artfynd.xlsx
+++ b/artfynd/A 978-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154307</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154308</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,8 +1065,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131154309</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>